--- a/sample_data/sample_members.xlsx
+++ b/sample_data/sample_members.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>member_code</t>
   </si>
@@ -34,34 +34,22 @@
     <t>M002</t>
   </si>
   <si>
-    <t>M003</t>
-  </si>
-  <si>
     <t>Member One</t>
   </si>
   <si>
     <t>Member Two</t>
   </si>
   <si>
-    <t>Member Three</t>
-  </si>
-  <si>
     <t>0700000001</t>
   </si>
   <si>
     <t>0700000002</t>
   </si>
   <si>
-    <t>0700000003</t>
-  </si>
-  <si>
     <t>member1@example.com</t>
   </si>
   <si>
     <t>member2@example.com</t>
-  </si>
-  <si>
-    <t>member3@example.com</t>
   </si>
 </sst>
 </file>
@@ -419,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -441,13 +429,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -455,27 +443,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
